--- a/reports/universe_2026-07-31.xlsx
+++ b/reports/universe_2026-07-31.xlsx
@@ -314,10 +314,10 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31 15:42 local</t>
+          <t>2026-07-31 16:33 local</t>
         </is>
       </c>
     </row>
@@ -29625,7 +29625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -29753,248 +29753,470 @@
       </c>
     </row>
     <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>CALL</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-18 $45</t>
-        </is>
-      </c>
-      <c r="E2" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="G2" s="60" t="n">
-        <v>2460</v>
-      </c>
-      <c r="H2" s="27" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I2" s="28" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J2" s="28" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="K2" s="25" t="inlineStr">
-        <is>
-          <t>PASS: delta +0.76 outside 0.60-0.75 band</t>
-        </is>
-      </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18 $350</t>
+        </is>
+      </c>
+      <c r="E2" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="G2" s="61" t="n">
+        <v>2405</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>360.07</v>
+      </c>
+      <c r="I2" s="22" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J2" s="22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="K2" s="19" t="inlineStr">
+        <is>
+          <t>PASS: PRIME SETUP: volatility compressed (squeeze 2th pctile) AND premium cheap vs realized (IV/RV 1.18) - the textbook long-options pairing</t>
+        </is>
+      </c>
+      <c r="L2" s="19" t="inlineStr">
+        <is>
+          <t>PRIME 60</t>
+        </is>
+      </c>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="21" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q2" s="21" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="R2" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S2" s="19" t="inlineStr">
+        <is>
+          <t>PLANNED - fills ~8:50 AM</t>
+        </is>
+      </c>
+      <c r="T2" s="19" t="inlineStr">
+        <is>
+          <t>The night's only clean full-gate CALL: GE passed every equity gate on the 7/31 universe run and was already first in line from 7/30, when the only blocker was sizing (no compliant contract fit the cap). Today's rally to ~360 fixed that WITHOUT the new exception: the Sep 350 call now carries live TradeStation delta 0.63 at a $2,405 mid - inside the original $2,500 cap, cap_exception NOT needed. PRIME SETUP: Bollinger band width in the 2nd percentile of the last 120 sessions (tight coil) with implied vol only 1.18x realized - cheap premium on stored energy, the exact pairing the playbook prefers. Readiness 60, highest scored tonight (volume flow at a fresh 20-day extreme with the trade). Needs +8.5% by the time exit to double vs a 13.7% expected move - fits. Earnings ~10/20, a month AFTER expiry. OI 2,234, close spread 8.7%. FILL NOTE: tomorrow is SATURDAY - the morning routine fills this at the live mid MONDAY 8/3 at 8:50 CT (macro calendar clear that day). Sell at $48.10 (premium doubled), cut at $12.05 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips SELL on GE - exit early regardless of premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18 $105</t>
+        </is>
+      </c>
+      <c r="E3" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G3" s="61" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K3" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M2" s="27" t="n">
-        <v>4.775</v>
-      </c>
-      <c r="N2" s="26" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O2" s="60" t="n">
-        <v>-72</v>
-      </c>
-      <c r="P2" s="27" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="Q2" s="27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R2" s="25" t="inlineStr">
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="21" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q3" s="21" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S2" s="25" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="T2" s="25" t="inlineStr">
-        <is>
-          <t>Energy with the Middle East supply premium at its back: oil E&amp;P group +3.4% on Fed day while nearly everything else bled, SLB in buy mode with a full gate pass, earnings behind it (reported mid-July, next mid-Oct after expiry). The most liquid chain of tonight's three: OI 8,143 on this strike, 7.1% spread. Deep-ITM Sep call, delta est ~0.72 (estimated - TS greeks offline after hours, verify tomorrow). Sell at $9.85 (premium doubled), cut at $2.45 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips SELL on SLB - exit early regardless of premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="55" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B3" s="55" t="inlineStr">
-        <is>
-          <t>DHI</t>
-        </is>
-      </c>
-      <c r="C3" s="56" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="D3" s="56" t="inlineStr">
-        <is>
-          <t>2026-09-18 $150</t>
-        </is>
-      </c>
-      <c r="E3" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="57" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G3" s="59" t="n">
-        <v>1840</v>
-      </c>
-      <c r="H3" s="57" t="n">
-        <v>147.16</v>
-      </c>
-      <c r="I3" s="61" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="J3" s="61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K3" s="56" t="inlineStr">
-        <is>
-          <t>REJECT: spread 15.2% &gt; 15% - mid fill not realistic</t>
-        </is>
-      </c>
-      <c r="L3" s="56" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="M3" s="57" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="N3" s="58" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="O3" s="59" t="n">
-        <v>190</v>
-      </c>
-      <c r="P3" s="57" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Q3" s="57" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R3" s="56" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="S3" s="56" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="T3" s="56" t="inlineStr">
-        <is>
-          <t>Rate-victim short: the Fed just priced TWO more hikes, homebuilders fell 3.7% as a group, DHI -2.7% closing near its low, in sell mode on the scan. The bet is mortgage-rate repricing keeps grinding builders down into fall. Earnings behind it (reported 7/21, next late Oct after expiry). DEVIATIONS logged at entry: chain is thin - the 150 strike is the ONLY one passing the OI-100 rule (OI 122); spread 15.2% at the close, wide; delta est ~-0.57, a touch under the 0.60 floor - closest compliant strike. Greeks estimated (TS offline), verify tomorrow. Sell at $18.40 (premium doubled), cut at $4.60 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips BUY on DHI - exit early regardless of premium.</t>
+      <c r="S3" s="19" t="inlineStr">
+        <is>
+          <t>PLANNED - fills ~8:50 AM</t>
+        </is>
+      </c>
+      <c r="T3" s="19" t="inlineStr">
+        <is>
+          <t>Sector-rolling short, the cleanest chain of the night. Catalyst: semiconductors are the worst-decelerating group on the rotation radar - SMH state ROLLING with acceleration -20.0 (worst on the board), -14.8% on the month, -5.9% on the week - and INTC is in sell mode on the scan, still ~9% above its 20-day low so the down-leg has room. Earnings 10/22, five weeks AFTER expiry - clear. Chain quality is the draw: OI 8,278, spread 2.5%, and the put costs only 0.91x what the stock actually moves (IV/RV) - not paying up for a crowded short. Live TS delta -0.64. Needs -27.9% to double vs a 28.0% expected move - a full-throated breakdown bet, sized small at $1,990. FILL NOTE: tomorrow is SATURDAY - morning routine fills at the live mid MONDAY 8/3 at 8:50 CT. Sell at $39.80 (premium doubled), cut at $9.95 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips BUY on INTC or SMH leaves ROLLING - exit early regardless of premium.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>2026-09-18 $250</t>
-        </is>
-      </c>
-      <c r="E4" s="62" t="n">
+          <t>2026-09-18 $325</t>
+        </is>
+      </c>
+      <c r="E4" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>19.48</v>
-      </c>
-      <c r="G4" s="62" t="n">
-        <v>1948</v>
+        <v>20.75</v>
+      </c>
+      <c r="G4" s="61" t="n">
+        <v>2075</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>265.53</v>
+        <v>308.91</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>0.74</v>
+        <v>-0.66</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K4" s="19" t="inlineStr">
         <is>
-          <t>FLAG: spread 13.6% (10-15%) - watch fill quality</t>
+          <t>FLAG: spread 12.0% (10-15%) - watch fill quality</t>
         </is>
       </c>
       <c r="L4" s="19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M4" s="19" t="n"/>
       <c r="N4" s="19" t="n"/>
       <c r="O4" s="19" t="n"/>
       <c r="P4" s="21" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>PLANNED - fills ~8:50 AM</t>
+        </is>
+      </c>
+      <c r="T4" s="19" t="inlineStr">
+        <is>
+          <t>Megacap-tech rolling short. Catalyst: broad tech (XLK) is ROLLING on the rotation radar (acceleration -9.5, -6.1% on the month) and AAPL is in sell mode on the scan, sitting just 2.9% above its 20-day low with momentum (MACD histogram) already turned down. The put is CHEAP: implied vol is only 0.71x the stock's realized movement - the market is underpricing how much AAPL actually moves. Needs only -8.4% by the time exit to double vs a 9.7% expected move. Earnings 10/29, six weeks AFTER expiry - clear. Live TS delta -0.71, OI 2,856, 1,047 contracts traded today. FLAG: 12% close spread - watch fill quality (the two-step morning fill at the live mid is the protection). CONCENTRATION NOTE: 2nd of max 2 in tech-rotation-short with INTC - the theme cap is now FULL. FILL NOTE: tomorrow is SATURDAY - morning routine fills at the live mid MONDAY 8/3 at 8:50 CT. Sell at $41.50 (premium doubled), cut at $10.40 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips BUY on AAPL or XLK leaves ROLLING - exit early regardless of premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>2026-09-18 $45</t>
+        </is>
+      </c>
+      <c r="E5" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="57" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G5" s="59" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H5" s="57" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="I5" s="62" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J5" s="62" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K5" s="56" t="inlineStr">
+        <is>
+          <t>PASS: delta +0.76 outside 0.60-0.75 band</t>
+        </is>
+      </c>
+      <c r="L5" s="56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M5" s="57" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N5" s="58" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O5" s="59" t="n">
+        <v>265</v>
+      </c>
+      <c r="P5" s="57" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="Q5" s="57" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R5" s="56" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S5" s="56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T5" s="56" t="inlineStr">
+        <is>
+          <t>Energy with the Middle East supply premium at its back: oil E&amp;P group +3.4% on Fed day while nearly everything else bled, SLB in buy mode with a full gate pass, earnings behind it (reported mid-July, next mid-Oct after expiry). The most liquid chain of tonight's three: OI 8,143 on this strike, 7.1% spread. Deep-ITM Sep call, delta est ~0.72 (estimated - TS greeks offline after hours, verify tomorrow). Sell at $9.85 (premium doubled), cut at $2.45 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips SELL on SLB - exit early regardless of premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>DHI</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>2026-09-18 $150</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G6" s="59" t="n">
+        <v>1840</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>147.16</v>
+      </c>
+      <c r="I6" s="62" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="J6" s="62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="56" t="inlineStr">
+        <is>
+          <t>REJECT: spread 15.2% &gt; 15% - mid fill not realistic</t>
+        </is>
+      </c>
+      <c r="L6" s="56" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="N6" s="58" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O6" s="59" t="n">
+        <v>190</v>
+      </c>
+      <c r="P6" s="57" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q6" s="57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R6" s="56" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S6" s="56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T6" s="56" t="inlineStr">
+        <is>
+          <t>Rate-victim short: the Fed just priced TWO more hikes, homebuilders fell 3.7% as a group, DHI -2.7% closing near its low, in sell mode on the scan. The bet is mortgage-rate repricing keeps grinding builders down into fall. Earnings behind it (reported 7/21, next late Oct after expiry). DEVIATIONS logged at entry: chain is thin - the 150 strike is the ONLY one passing the OI-100 rule (OI 122); spread 15.2% at the close, wide; delta est ~-0.57, a touch under the 0.60 floor - closest compliant strike. Greeks estimated (TS offline), verify tomorrow. Sell at $18.40 (premium doubled), cut at $4.60 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips BUY on DHI - exit early regardless of premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18 $250</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="G7" s="61" t="n">
+        <v>1948</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>265.53</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>FLAG: spread 13.6% (10-15%) - watch fill quality</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="21" t="n">
         <v>38.95</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q7" s="21" t="n">
         <v>9.75</v>
       </c>
-      <c r="R4" s="19" t="inlineStr">
+      <c r="R7" s="19" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S4" s="19" t="inlineStr">
+      <c r="S7" s="19" t="inlineStr">
         <is>
           <t>VOIDED (no-chase rule)</t>
         </is>
       </c>
-      <c r="T4" s="19" t="inlineStr">
+      <c r="T7" s="19" t="inlineStr">
         <is>
           <t>Top gate pass of Fed day: defensive healthcare leadership in a two-hikes world, fresh 7/24 buy signal, buyers dominant (+DI 30 vs 12), earnings behind it (next report mid-Oct, AFTER this option expires). Deep-ITM Sep call, delta est ~0.70 at the close. CAVEATS logged at entry: stock slipped ~2% after hours on no company news (broad post-META drift) - entry premium is the 4PM closing mid, conservative/rich vs the likely open; TradeStation greeks were offline after hours so delta is estimated from moneyness, verify on tomorrow's live chain. OI 5,628, spread 13.6% at the close. Sell at $38.95 (premium doubled), cut at $9.75 (premium halved), or out by 2026-08-28 (21 days to expiry) no matter what. Thesis break = daily Chandelier flips SELL on JNJ - exit early regardless of premium.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>SCORECARD: 0 closed (0 winners), paper-banked +0. 2 open, marking +118. 1 voided by the no-chase rule - logged, counted in the Friday review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>SCORECARD: 0 closed (0 winners), paper-banked +0. 2 open, marking +455. 3 planned (fill at next open). 1 voided by the no-chase rule - logged, counted in the Friday review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>PAPER TRADING ONLY - not one real dollar goes into options until this tab shows a positive record over enough trades to mean something. Long calls and long puts only; the premium paid is the whole risk. Picks come from names that passed the day's gates, contracts are chosen in-the-money leaning (delta ~0.60-0.75), 45-90 days out, liquid strikes only, and every trade gets its take-profit, stop, and exit-by date set AT ENTRY. TWO-STEP TIMING: the evening run SELECTS (status PLANNED); the morning routine ~8:50 AM fills at the live TradeStation midpoint - or VOIDS the pick if it gapped &gt;2% against us, costs &gt;20% more than planned, or no longer passes the standards. Daily marks use end-of-day midpoints.</t>
         </is>
@@ -30222,7 +30444,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-07-31 15:42 local</t>
+          <t>2026-07-31 16:33 local</t>
         </is>
       </c>
     </row>
@@ -30312,7 +30534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -31444,209 +31666,321 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>XNCR LOADED @ 21.49 (Health Technology)  -  d60 +5.1%, ADX 58</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>PBF LOADED @ 73.10 (Energy Minerals)  -  d60 +10.7%, ADX 50</t>
+          <t>(ignition sweep state not found - see Data Quality tab)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>TXG LOADED @ 49.43 (Health Technology)  -  d60 +2.9%, ADX 46</t>
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>ROTATION RADAR</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>DK LOADED @ 67.71 (Energy Minerals)  -  d60 +0.8%, ADX 45</t>
-        </is>
-      </c>
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>1 Week %</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>1 Month %</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>6 Month %</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>ORKA LOADED @ 97.86 (Health Technology)  -  d60 +2.8%, ADX 39</t>
-        </is>
-      </c>
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>China internet</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>IGNITING</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D61" s="15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="G61" s="15" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CORT LOADED @ 118.32 (Health Technology)  -  d60 +22.4%, ADX 36</t>
-        </is>
-      </c>
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Oil E&amp;P</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>IGNITING</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G62" s="15" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>BFH LOADED @ 110.62 (Finance)  -  d60 +1.7%, ADX 25</t>
-        </is>
-      </c>
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>IGNITING</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G63" s="15" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BRKR LOADED @ 64.34 (Health Technology)  -  d60 +2.3%, ADX 24</t>
-        </is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>18.4</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>ROTATION RADAR</t>
-        </is>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oil services</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>Acceleration</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>1 Week %</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>1 Month %</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>6 Month %</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="n"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gold miners</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-25.1</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>China internet</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>IGNITING</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="D68" s="15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F68" s="15" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="G68" s="15" t="n"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t>Oil E&amp;P</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>IGNITING</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D69" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F69" s="15" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="G69" s="15" t="n"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>IGNITING</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D70" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F70" s="15" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G70" s="15" t="n"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="F71" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Regional banks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31655,22 +31989,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>-0.1</v>
       </c>
       <c r="D72" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="F72" t="n">
-        <v>18.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Oil services</t>
+          <t>Discretionary</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31679,22 +32013,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.5</v>
+        <v>-0.7</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9</v>
+        <v>6.4</v>
       </c>
       <c r="E73" t="n">
-        <v>4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="F73" t="n">
-        <v>11.2</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Gold miners</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -31703,22 +32037,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.4</v>
+        <v>-1</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="F74" t="n">
-        <v>-25.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Defense/aero</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -31727,22 +32061,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>-2.1</v>
       </c>
       <c r="D75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F75" t="n">
         <v>3.7</v>
-      </c>
-      <c r="E75" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Metals/mining</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -31751,22 +32085,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="D76" t="n">
-        <v>7.1</v>
+        <v>-2.9</v>
       </c>
       <c r="E76" t="n">
-        <v>2.4</v>
+        <v>-5</v>
       </c>
       <c r="F76" t="n">
-        <v>2.9</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -31775,22 +32109,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>-4.4</v>
       </c>
       <c r="E77" t="n">
-        <v>2.4</v>
+        <v>-2</v>
       </c>
       <c r="F77" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Biotech (cap-wt)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -31799,22 +32133,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="E78" t="n">
-        <v>1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="F78" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Regional banks</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -31823,22 +32157,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.1</v>
+        <v>-3.6</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F79" t="n">
-        <v>10.6</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -31847,22 +32181,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.7</v>
+        <v>-4</v>
       </c>
       <c r="D80" t="n">
-        <v>6.4</v>
+        <v>-1.1</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.4</v>
+        <v>-2.5</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Transports</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -31871,22 +32205,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1</v>
+        <v>-4.3</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2</v>
+        <v>-3.7</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
       <c r="F81" t="n">
-        <v>2.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Defense/aero</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -31895,22 +32229,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-2.1</v>
+        <v>-5.6</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3</v>
+        <v>-4.5</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.5</v>
+        <v>-11</v>
       </c>
       <c r="F82" t="n">
-        <v>3.7</v>
+        <v>-31.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Metals/mining</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -31919,22 +32253,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-2.2</v>
+        <v>-6</v>
       </c>
       <c r="D83" t="n">
-        <v>-2.9</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>-5</v>
+        <v>-7.1</v>
       </c>
       <c r="F83" t="n">
-        <v>-17</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Homebuilders</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -31943,94 +32277,97 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-2.4</v>
+        <v>-7.9</v>
       </c>
       <c r="D84" t="n">
-        <v>-4.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E84" t="n">
-        <v>-2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>2.6</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Biotech (cap-wt)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="F85" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Airlines</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="F85" s="16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G85" s="16" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="D86" t="n">
-        <v>4</v>
-      </c>
-      <c r="E86" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F86" t="n">
-        <v>32.5</v>
-      </c>
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Tech broad</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="F86" s="16" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G86" s="16" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>-4</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="F87" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>Biotech (eq-wt)</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Transports</t>
+          <t>Spec growth</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -32039,217 +32376,46 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-4.3</v>
+        <v>-10.2</v>
       </c>
       <c r="D88" t="n">
-        <v>-3.7</v>
+        <v>-3.4</v>
       </c>
       <c r="E88" t="n">
-        <v>-2.4</v>
+        <v>-11.4</v>
       </c>
       <c r="F88" t="n">
-        <v>10.9</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-11</v>
-      </c>
-      <c r="F89" t="n">
-        <v>-31.9</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Robotics</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>-6</v>
-      </c>
-      <c r="D90" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>-6.4</v>
-      </c>
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Semis</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G89" s="16" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Homebuilders</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Airlines</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>ROLLING</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="D92" s="16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="F92" s="16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="G92" s="16" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>Tech broad</t>
-        </is>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>ROLLING</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="D93" s="16" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="F93" s="16" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G93" s="16" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>Biotech (eq-wt)</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>ROLLING</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D94" s="16" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="F94" s="16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G94" s="16" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Spec growth</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="E95" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-7.4</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Semis</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>ROLLING</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="n">
-        <v>-20</v>
-      </c>
-      <c r="D96" s="16" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="F96" s="16" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="G96" s="16" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
         <is>
           <t>READ THIS BEFORE ACTING ON THE TABLE ABOVE: these states were back-tested and came out BACKWARDS - groups flagged as heating up did NOT go on to outperform. Two same-week proofs: energy went IGNITING on 7/24 and was demoted one session later on 7/27; airlines were demoted to ROLLING on 7/27, the day airlines were the second-best group in the market at +2.9%. Use this to see WHERE YOU ARE EXPOSED. Never as a reason to buy or sell.</t>
         </is>
@@ -32866,7 +33032,7 @@
         <v>60.9</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R6" s="20" t="n">
         <v>78.09999999999999</v>
@@ -32954,7 +33120,7 @@
         <v>55.5</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R7" s="20" t="n">
         <v>94</v>
@@ -33042,7 +33208,7 @@
         <v>51.7</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="R8" s="20" t="n">
         <v>86.59999999999999</v>
@@ -33136,7 +33302,7 @@
         <v>62.5</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="R9" s="20" t="n">
         <v>92.8</v>
@@ -33754,7 +33920,7 @@
         <v>53.3</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="R16" s="26" t="n">
         <v>91.40000000000001</v>
@@ -34294,7 +34460,7 @@
         <v>50.4</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>58.1</v>
@@ -34730,7 +34896,7 @@
         <v>54.9</v>
       </c>
       <c r="Q27" s="28" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>63.6</v>
@@ -34818,7 +34984,7 @@
         <v>57.5</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>56.2</v>
@@ -35102,7 +35268,7 @@
         <v>55.2</v>
       </c>
       <c r="Q31" s="28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R31" s="26" t="n">
         <v>88.2</v>
@@ -35190,7 +35356,7 @@
         <v>54.5</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="R32" s="26" t="n">
         <v>81.7</v>
@@ -35462,7 +35628,7 @@
         <v>45.8</v>
       </c>
       <c r="Q35" s="28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>90.3</v>
@@ -35982,7 +36148,7 @@
         <v>56.5</v>
       </c>
       <c r="Q41" s="28" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="R41" s="26" t="n">
         <v>57.1</v>
@@ -36070,7 +36236,7 @@
         <v>48.3</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R42" s="26" t="n">
         <v>90.7</v>
@@ -36268,7 +36434,7 @@
         <v>52.4</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R44" s="26" t="n">
         <v>79.5</v>
@@ -36356,7 +36522,7 @@
         <v>49</v>
       </c>
       <c r="Q45" s="28" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="R45" s="26" t="n">
         <v>79.2</v>
@@ -36540,7 +36706,7 @@
         <v>58.6</v>
       </c>
       <c r="Q47" s="28" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="R47" s="26" t="n">
         <v>96.40000000000001</v>
@@ -36642,7 +36808,7 @@
         <v>50.7</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>93.90000000000001</v>
@@ -38272,7 +38438,7 @@
         <v>52.1</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="R66" s="26" t="n">
         <v>59.6</v>
@@ -38464,7 +38630,7 @@
         <v>55.8</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="R68" s="26" t="n">
         <v>94.40000000000001</v>
@@ -39088,7 +39254,7 @@
         <v>48.1</v>
       </c>
       <c r="Q75" s="28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R75" s="26" t="n">
         <v>74.09999999999999</v>
@@ -39448,7 +39614,7 @@
         <v>44.9</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R79" s="26" t="n">
         <v>70.90000000000001</v>

--- a/reports/universe_2026-07-31.xlsx
+++ b/reports/universe_2026-07-31.xlsx
@@ -1775,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01 16:01 local</t>
+          <t>2026-08-01 16:09 local</t>
         </is>
       </c>
     </row>
@@ -2314,77 +2314,89 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Readiness 0-100 = poised-to-move (UNCALIBRATED - ranks, does not veto). The gates answer 'is it SAFE to buy'; this answers 'does it MOVE soon'. Five checks worth 20 points each: bands coiled tight, price within reach of its trigger (the 20-day high), volume flowing in, momentum turning up, beating the market. HOW TO READ IT: 60+ = the spring is loading. Below 40 = expect sideways first - DGX read 26/100 the night it topped the gate list on trend strength (ADX 42) and then went nowhere, exactly as scored (the 7/31 post-mortem that created this column). The text after the number names the strongest or weakest ingredients. It RANKS which candidate to look at first; it never blocks a trade on its own until the Friday reviews prove it deserves that power. 'n/a' = the overnight scoring step did not run for that name.</t>
+          <t>Poised-to-move score. The gates answer 'is it SAFE to buy'; this answers 'is a move LOADING soon, in the trade's direction'. Five classic ready-to-run checks, 20 points each: (1) SQUEEZE - price bands coiled to their tightest in months = energy stored, the closest thing to a true 'ready' signal; (2) TRIGGER - how close price sits to its 20-day high, i.e. how short the fuse is (one good day vs a long grind); (3) VOLUME - quiet accumulation: big money sneaking in while price goes sideways; (4) MOMENTUM - the turn before the turn: momentum just changed direction toward the trade; (5) RELATIVE STRENGTH - beating the market at a 60-day extreme, money singling this name out right now. The text after the number names the lit and dead ingredients - READ THE TEXT, not just the number: a 54 built on 'tight coil + volume' is a different animal from a 54 built on 'strong but bands blown out'. 'n/a' = the overnight scoring step did not run for that name.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Magical (CCI-20)</t>
+          <t>Readiness - the levels</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Above +100 = overbought, below -100 = oversold. NOTE: measured 2026-07-22 across 1,725 signals, this cut does NOT separate returns (0.03pt over 21 days). Treat as context, not a veto.</t>
+          <t>UNDER ~30 = RESTING: energy already spent (bands wide after a move) or nothing loading - expect sideways unless news does the work; a fine HOLDING can score here (DGX read 26 and beat the market that week while going nowhere vs its entry). 40-60 = MIXED: two or three parts lit - the driver text decides whether it's interesting. 70+ = RARE/COILED: most parts firing together; CORT hit 95 on 7/7 and ran +22%. PRIME SETUP tag (options tab) = tight squeeze + cheap premium at once - the one pattern with real published history. NOW THE HONEST PART (first calibration look, 2026-08-01): comparing the big skipped runners vs skipped picks that went NOWHERE, pick-day scores showed NO separation (means 47 vs 43) - PSA scored 80 and never moved 2%; CAKE scored 16 and ran +30% on earnings. The score sees STORED ENERGY only - it is blind to catalyst movers (news, earnings gaps) and says nothing about direction or exact timing. So it works BOTH ways: a high score is NOT a green light and a low score is NOT a veto. Use it to decide which gate-passer to LOOK AT first and what posture you're buying (coiled vs resting), never as the reason to trade. The nightly scan is collecting the forward evidence; Friday reviews decide if any threshold ever earns real power.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ZLSMA-50</t>
+          <t>Magical (CCI-20)</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>The trend line. Price below it on a buy signal is a structural fail.</t>
+          <t>Above +100 = overbought, below -100 = oversold. NOTE: measured 2026-07-22 across 1,725 signals, this cut does NOT separate returns (0.03pt over 21 days). Treat as context, not a veto.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Chandelier Exit</t>
+          <t>ZLSMA-50</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Flips BUY/SELL. The label price is the STOP level, not an entry.</t>
+          <t>The trend line. Price below it on a buy signal is a structural fail.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Regime PASS</t>
+          <t>Chandelier Exit</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Above a rising 200-day and beating SPY -&gt; normal size.</t>
+          <t>Flips BUY/SELL. The label price is the STOP level, not an entry.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>Regime PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Above a rising 200-day and beating SPY -&gt; normal size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
           <t>Regime REPAIR</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Below the 200-day -&gt; starter size only.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Regime DEEP-FAIL</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>More than 10% below the 200-day -&gt; watch only, no size.</t>
         </is>
@@ -30747,7 +30759,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01 16:01 local</t>
+          <t>2026-08-01 16:09 local</t>
         </is>
       </c>
     </row>

--- a/reports/universe_2026-07-31.xlsx
+++ b/reports/universe_2026-07-31.xlsx
@@ -23,8 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 - Run Summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 - Fresh Buys'!$A$1:$AA$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2b - Gated Longs'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 - Fresh Buys'!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2b - Gated Longs'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3 - Plans'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4 - Blocked'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5 - Sell Mode'!$A$1:$M$1</definedName>
@@ -964,11 +964,17 @@
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
+        <t>RESTED LEADER = this name fits the pre-registered second-leg profile tonight: proven trend (ADX 25+), buyers firmly in control (DI margin 10+), RESTING (readiness &lt;=30) on quiet volume (RVOL &lt;1.2). July's +15% winners were overwhelmingly this shape - NOT coiled squeezes. ON TRIAL (an experiment, verdict 2026-09-25): the tag carries ZERO weight in gates, sizing or ranking until the forward test proves it. Blank = does not fit the profile tonight - not a defect.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
         <t>Next scheduled catalyst for this name - earnings within 7 days, or a Phase-3 trial readout window. Blank = none flagged. From build_catalyst_calendar.py.
 (Full guide: 'READ ME FIRST' tab)</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>What the catalyst is and the suggested ACTION. Earnings: trim into the print, re-enter post-print only if it beats AND holds (PEAD). Biopharma: BINARY - defined-risk / awareness only, never hold a momentum long through it.
 (Full guide: 'READ ME FIRST' tab)</t>
@@ -1058,11 +1064,17 @@
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
+        <t>RESTED LEADER = this name fits the pre-registered second-leg profile tonight: proven trend (ADX 25+), buyers firmly in control (DI margin 10+), RESTING (readiness &lt;=30) on quiet volume (RVOL &lt;1.2). July's +15% winners were overwhelmingly this shape - NOT coiled squeezes. ON TRIAL (an experiment, verdict 2026-09-25): the tag carries ZERO weight in gates, sizing or ranking until the forward test proves it. Blank = does not fit the profile tonight - not a defect.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
         <t>Next scheduled catalyst for this name - earnings within 7 days, or a Phase-3 trial readout window. Blank = none flagged. From build_catalyst_calendar.py.
 (Full guide: 'READ ME FIRST' tab)</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t>What the catalyst is and the suggested ACTION. Earnings: trim into the print, re-enter post-print only if it beats AND holds (PEAD). Biopharma: BINARY - defined-risk / awareness only, never hold a momentum long through it.
 (Full guide: 'READ ME FIRST' tab)</t>
@@ -1826,7 +1838,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01 16:09 local</t>
+          <t>2026-08-01 17:32 local</t>
         </is>
       </c>
     </row>
@@ -30759,7 +30771,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01 16:09 local</t>
+          <t>2026-08-01 17:32 local</t>
         </is>
       </c>
     </row>
@@ -32760,7 +32772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA79"/>
+  <dimension ref="A1:AB79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -32788,8 +32800,9 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="26" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="62" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="62" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -32920,10 +32933,15 @@
       </c>
       <c r="Z1" s="12" t="inlineStr">
         <is>
+          <t>Rested Leader</t>
+        </is>
+      </c>
+      <c r="AA1" s="12" t="inlineStr">
+        <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="AA1" s="12" t="inlineStr">
+      <c r="AB1" s="12" t="inlineStr">
         <is>
           <t>Catalyst View</t>
         </is>
@@ -33025,8 +33043,9 @@
           <t>Passes every gate: regime, trend strength (ADX)&gt;=20, +DI&gt;-DI, above its trend line (ZLSMA), and liquid enough for a $85,000 position.</t>
         </is>
       </c>
-      <c r="Z2" s="19" t="inlineStr"/>
+      <c r="Z2" s="19" t="n"/>
       <c r="AA2" s="19" t="inlineStr"/>
+      <c r="AB2" s="19" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="17" t="n">
@@ -33124,8 +33143,9 @@
           <t>Passes every gate: regime, trend strength (ADX)&gt;=20, +DI&gt;-DI, above its trend line (ZLSMA), and liquid enough for a $85,000 position.</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr"/>
+      <c r="Z3" s="19" t="n"/>
       <c r="AA3" s="19" t="inlineStr"/>
+      <c r="AB3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="17" t="n">
@@ -33223,8 +33243,9 @@
           <t>regime REPAIR (23.0346% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="Z4" s="19" t="inlineStr"/>
+      <c r="Z4" s="19" t="n"/>
       <c r="AA4" s="19" t="inlineStr"/>
+      <c r="AB4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="17" t="n">
@@ -33322,8 +33343,9 @@
           <t>Passes every gate: regime, trend strength (ADX)&gt;=20, +DI&gt;-DI, above its trend line (ZLSMA), and liquid enough for a $85,000 position.</t>
         </is>
       </c>
-      <c r="Z5" s="19" t="inlineStr"/>
+      <c r="Z5" s="19" t="n"/>
       <c r="AA5" s="19" t="inlineStr"/>
+      <c r="AB5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="17" t="n">
@@ -33415,8 +33437,9 @@
           <t>regime REPAIR (8.4497% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="Z6" s="19" t="inlineStr"/>
+      <c r="Z6" s="19" t="n"/>
       <c r="AA6" s="19" t="inlineStr"/>
+      <c r="AB6" s="19" t="inlineStr"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="17" t="n">
@@ -33508,8 +33531,9 @@
           <t>Passes every gate: regime, trend strength (ADX)&gt;=20, +DI&gt;-DI, above its trend line (ZLSMA), and liquid enough for a $85,000 position.</t>
         </is>
       </c>
-      <c r="Z7" s="19" t="inlineStr"/>
+      <c r="Z7" s="19" t="n"/>
       <c r="AA7" s="19" t="inlineStr"/>
+      <c r="AB7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="17" t="n">
@@ -33607,8 +33631,9 @@
           <t>Passes every gate: regime, trend strength (ADX)&gt;=20, +DI&gt;-DI, above its trend line (ZLSMA), and liquid enough for a $85,000 position.</t>
         </is>
       </c>
-      <c r="Z8" s="19" t="inlineStr"/>
+      <c r="Z8" s="19" t="n"/>
       <c r="AA8" s="19" t="inlineStr"/>
+      <c r="AB8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="17" t="n">
@@ -33700,8 +33725,9 @@
           <t>regime REPAIR (11.8104% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="Z9" s="19" t="inlineStr"/>
+      <c r="Z9" s="19" t="n"/>
       <c r="AA9" s="19" t="inlineStr"/>
+      <c r="AB9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="23" t="n">
@@ -33799,8 +33825,9 @@
           <t>stop is 14.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
-      <c r="Z10" s="25" t="inlineStr"/>
+      <c r="Z10" s="25" t="n"/>
       <c r="AA10" s="25" t="inlineStr"/>
+      <c r="AB10" s="25" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="23" t="n">
@@ -33892,8 +33919,9 @@
           <t>stop is 5.81x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 17.5% away - volatility...</t>
         </is>
       </c>
-      <c r="Z11" s="25" t="inlineStr"/>
+      <c r="Z11" s="25" t="n"/>
       <c r="AA11" s="25" t="inlineStr"/>
+      <c r="AB11" s="25" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="23" t="n">
@@ -33985,8 +34013,9 @@
           <t>-DI 22.0013 &gt;= +DI 20.7429 - sellers in control; stop is 4.70x ATR (multiples of a normal day's swing) - so wide the position shrinks to a toke...</t>
         </is>
       </c>
-      <c r="Z12" s="25" t="inlineStr"/>
+      <c r="Z12" s="25" t="n"/>
       <c r="AA12" s="25" t="inlineStr"/>
+      <c r="AB12" s="25" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="23" t="n">
@@ -34084,8 +34113,9 @@
           <t>stop is 4.92x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 31.8% away - volatility...</t>
         </is>
       </c>
-      <c r="Z13" s="25" t="inlineStr"/>
+      <c r="Z13" s="25" t="n"/>
       <c r="AA13" s="25" t="inlineStr"/>
+      <c r="AB13" s="25" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="23" t="n">
@@ -34177,8 +34207,9 @@
           <t>stop is 15.1% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
-      <c r="Z14" s="25" t="inlineStr"/>
+      <c r="Z14" s="25" t="n"/>
       <c r="AA14" s="25" t="inlineStr"/>
+      <c r="AB14" s="25" t="inlineStr"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="23" t="n">
@@ -34260,8 +34291,9 @@
           <t>trend strength (ADX) 17.7118 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z15" s="25" t="inlineStr"/>
+      <c r="Z15" s="25" t="n"/>
       <c r="AA15" s="25" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="23" t="n">
@@ -34359,8 +34391,9 @@
           <t>stop is 0.88x ATR (2.8687) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
         </is>
       </c>
-      <c r="Z16" s="25" t="inlineStr"/>
+      <c r="Z16" s="25" t="n"/>
       <c r="AA16" s="25" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="23" t="n">
@@ -34452,8 +34485,9 @@
           <t>trend strength (ADX) 19.0248 below 20 - no trend to ride; stop is 5.37x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceili...</t>
         </is>
       </c>
-      <c r="Z17" s="25" t="inlineStr"/>
+      <c r="Z17" s="25" t="n"/>
       <c r="AA17" s="25" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="23" t="n">
@@ -34545,8 +34579,9 @@
           <t>stop is 12.9% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
-      <c r="Z18" s="25" t="inlineStr"/>
+      <c r="Z18" s="25" t="n"/>
       <c r="AA18" s="25" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="23" t="n">
@@ -34644,8 +34679,9 @@
           <t>trend strength (ADX) 19.2408 below 20 - no trend to ride; stop is 13.5% away - volatility cap 12%: a name this wild shrinks ...</t>
         </is>
       </c>
-      <c r="Z19" s="25" t="inlineStr"/>
+      <c r="Z19" s="25" t="n"/>
       <c r="AA19" s="25" t="inlineStr"/>
+      <c r="AB19" s="25" t="inlineStr"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="23" t="n">
@@ -34737,8 +34773,9 @@
           <t>trend strength (ADX) 15.9956 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z20" s="25" t="inlineStr"/>
+      <c r="Z20" s="25" t="n"/>
       <c r="AA20" s="25" t="inlineStr"/>
+      <c r="AB20" s="25" t="inlineStr"/>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="23" t="n">
@@ -34830,8 +34867,9 @@
           <t>-DI 22.8119 &gt;= +DI 17.973 - sellers in control; stop is 18.9% away - volatility cap 12%: a name this wild s...</t>
         </is>
       </c>
-      <c r="Z21" s="25" t="inlineStr"/>
+      <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="25" t="inlineStr"/>
+      <c r="AB21" s="25" t="inlineStr"/>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="23" t="n">
@@ -34923,8 +34961,9 @@
           <t>regime DEEP-FAIL (-19.1307% vs the 200-day average) - watch only, no size</t>
         </is>
       </c>
-      <c r="Z22" s="25" t="inlineStr"/>
+      <c r="Z22" s="25" t="n"/>
       <c r="AA22" s="25" t="inlineStr"/>
+      <c r="AB22" s="25" t="inlineStr"/>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="23" t="n">
@@ -35016,8 +35055,9 @@
           <t>regime DEEP-FAIL (-21.3289% vs the 200-day average) - watch only, no size; -DI 21.5394 &gt;= +DI 15.2549 - sellers in control</t>
         </is>
       </c>
-      <c r="Z23" s="25" t="inlineStr"/>
+      <c r="Z23" s="25" t="n"/>
       <c r="AA23" s="25" t="inlineStr"/>
+      <c r="AB23" s="25" t="inlineStr"/>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="23" t="n">
@@ -35115,8 +35155,9 @@
           <t>-DI 19.8414 &gt;= +DI 18.5857 - sellers in control; stop is 15.2% away - volatility cap 12%: a name this wild ...</t>
         </is>
       </c>
-      <c r="Z24" s="25" t="inlineStr"/>
+      <c r="Z24" s="25" t="n"/>
       <c r="AA24" s="25" t="inlineStr"/>
+      <c r="AB24" s="25" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="23" t="n">
@@ -35198,8 +35239,9 @@
           <t>stop is 0.94x ATR (0.9547) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
         </is>
       </c>
-      <c r="Z25" s="25" t="inlineStr"/>
+      <c r="Z25" s="25" t="n"/>
       <c r="AA25" s="25" t="inlineStr"/>
+      <c r="AB25" s="25" t="inlineStr"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="23" t="n">
@@ -35291,8 +35333,9 @@
           <t>trend strength (ADX) 19.4768 below 20 - no trend to ride; stop is 0.85x ATR (13.4615) - inside daily noise, it gets hit by n...</t>
         </is>
       </c>
-      <c r="Z26" s="25" t="inlineStr"/>
+      <c r="Z26" s="25" t="n"/>
       <c r="AA26" s="25" t="inlineStr"/>
+      <c r="AB26" s="25" t="inlineStr"/>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="23" t="n">
@@ -35384,8 +35427,9 @@
           <t>stop is 12.3% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
-      <c r="Z27" s="25" t="inlineStr"/>
+      <c r="Z27" s="25" t="n"/>
       <c r="AA27" s="25" t="inlineStr"/>
+      <c r="AB27" s="25" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="23" t="n">
@@ -35477,12 +35521,13 @@
           <t>regime DEEP-FAIL (-29.1609% vs the 200-day average) - watch only, no size</t>
         </is>
       </c>
-      <c r="Z28" s="25" t="inlineStr">
+      <c r="Z28" s="25" t="n"/>
+      <c r="AA28" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="AA28" s="25" t="inlineStr">
+      <c r="AB28" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +2.91). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -35584,8 +35629,9 @@
           <t>trend strength (ADX) 17.5543 below 20 - no trend to ride; -DI 22.6262 &gt;= +DI 13.9685 - sellers in control; stop is 0.94x ATR (multiples of a normal day's swing)...</t>
         </is>
       </c>
-      <c r="Z29" s="25" t="inlineStr"/>
+      <c r="Z29" s="25" t="n"/>
       <c r="AA29" s="25" t="inlineStr"/>
+      <c r="AB29" s="25" t="inlineStr"/>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="23" t="n">
@@ -35683,8 +35729,9 @@
           <t>price 145.1075 at/below its trend line (ZLSMA) 148.9537 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z30" s="25" t="inlineStr"/>
+      <c r="Z30" s="25" t="n"/>
       <c r="AA30" s="25" t="inlineStr"/>
+      <c r="AB30" s="25" t="inlineStr"/>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="23" t="n">
@@ -35776,8 +35823,9 @@
           <t>trend strength (ADX) 18.9553 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z31" s="25" t="inlineStr"/>
+      <c r="Z31" s="25" t="n"/>
       <c r="AA31" s="25" t="inlineStr"/>
+      <c r="AB31" s="25" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="23" t="n">
@@ -35869,8 +35917,9 @@
           <t>trend strength (ADX) 19.9053 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z32" s="25" t="inlineStr"/>
+      <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="25" t="inlineStr"/>
+      <c r="AB32" s="25" t="inlineStr"/>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="23" t="n">
@@ -35962,8 +36011,9 @@
           <t>regime DEEP-FAIL (-16.4329% vs the 200-day average) - watch only, no size; stop is 13.9% away - volatility cap 12%: a n...</t>
         </is>
       </c>
-      <c r="Z33" s="25" t="inlineStr"/>
+      <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="25" t="inlineStr"/>
+      <c r="AB33" s="25" t="inlineStr"/>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="23" t="n">
@@ -36055,12 +36105,13 @@
           <t>regime DEEP-FAIL (-10.0651% vs the 200-day average) - watch only, no size; trend strength (ADX) 18.4779 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z34" s="25" t="inlineStr">
+      <c r="Z34" s="25" t="n"/>
+      <c r="AA34" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-06</t>
         </is>
       </c>
-      <c r="AA34" s="25" t="inlineStr">
+      <c r="AB34" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-06 (est EPS +2.89). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -36162,8 +36213,9 @@
           <t>trend strength (ADX) 19.4184 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z35" s="25" t="inlineStr"/>
+      <c r="Z35" s="25" t="n"/>
       <c r="AA35" s="25" t="inlineStr"/>
+      <c r="AB35" s="25" t="inlineStr"/>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="23" t="n">
@@ -36245,8 +36297,9 @@
           <t>trend strength (ADX) 18.9276 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z36" s="25" t="inlineStr"/>
+      <c r="Z36" s="25" t="n"/>
       <c r="AA36" s="25" t="inlineStr"/>
+      <c r="AB36" s="25" t="inlineStr"/>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="23" t="n">
@@ -36338,8 +36391,9 @@
           <t>regime DEEP-FAIL (-18.0618% vs the 200-day average) - watch only, no size; -DI 23.8609 &gt;= +DI 14.7481 - sellers in cont...</t>
         </is>
       </c>
-      <c r="Z37" s="25" t="inlineStr"/>
+      <c r="Z37" s="25" t="n"/>
       <c r="AA37" s="25" t="inlineStr"/>
+      <c r="AB37" s="25" t="inlineStr"/>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="23" t="n">
@@ -36431,8 +36485,9 @@
           <t>regime DEEP-FAIL (-25.9228% vs the 200-day average) - watch only, no size; trend strength (ADX) 16.5719 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z38" s="25" t="inlineStr"/>
+      <c r="Z38" s="25" t="n"/>
       <c r="AA38" s="25" t="inlineStr"/>
+      <c r="AB38" s="25" t="inlineStr"/>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="23" t="n">
@@ -36514,8 +36569,9 @@
           <t>trend strength (ADX) 11.5189 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z39" s="25" t="inlineStr"/>
+      <c r="Z39" s="25" t="n"/>
       <c r="AA39" s="25" t="inlineStr"/>
+      <c r="AB39" s="25" t="inlineStr"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="23" t="n">
@@ -36613,8 +36669,9 @@
           <t>price 17.075 at/below its trend line (ZLSMA) 18.102 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z40" s="25" t="inlineStr"/>
+      <c r="Z40" s="25" t="n"/>
       <c r="AA40" s="25" t="inlineStr"/>
+      <c r="AB40" s="25" t="inlineStr"/>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="23" t="n">
@@ -36706,8 +36763,9 @@
           <t>regime DEEP-FAIL (-12.4149% vs the 200-day average) - watch only, no size; trend strength (ADX) 17.1454 below 20 - no trend to ride</t>
         </is>
       </c>
-      <c r="Z41" s="25" t="inlineStr"/>
+      <c r="Z41" s="25" t="n"/>
       <c r="AA41" s="25" t="inlineStr"/>
+      <c r="AB41" s="25" t="inlineStr"/>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="23" t="n">
@@ -36805,12 +36863,13 @@
           <t>trend strength (ADX) 15.3446 below 20 - no trend to ride; -DI 17.2802 &gt;= +DI 16.2219 - sellers in control</t>
         </is>
       </c>
-      <c r="Z42" s="25" t="inlineStr">
+      <c r="Z42" s="25" t="n"/>
+      <c r="AA42" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-03</t>
         </is>
       </c>
-      <c r="AA42" s="25" t="inlineStr">
+      <c r="AB42" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-03 (est EPS +3.08). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -36906,12 +36965,13 @@
           <t>price 32.2557 at/below its trend line (ZLSMA) 33.6072 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z43" s="25" t="inlineStr">
+      <c r="Z43" s="25" t="n"/>
+      <c r="AA43" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="AA43" s="25" t="inlineStr">
+      <c r="AB43" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +0.32). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -37007,8 +37067,9 @@
           <t>price 248.34 at/below its trend line (ZLSMA) 267.7119 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z44" s="25" t="inlineStr"/>
+      <c r="Z44" s="25" t="n"/>
       <c r="AA44" s="25" t="inlineStr"/>
+      <c r="AB44" s="25" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="23" t="n">
@@ -37100,12 +37161,13 @@
           <t>regime DEEP-FAIL (-10.6727% vs the 200-day average) - watch only, no size; trend strength (ADX) 16.1533 below 20 - no trend to ride; sto...</t>
         </is>
       </c>
-      <c r="Z45" s="25" t="inlineStr">
+      <c r="Z45" s="25" t="n"/>
+      <c r="AA45" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="AA45" s="25" t="inlineStr">
+      <c r="AB45" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +3.32). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -37201,8 +37263,9 @@
           <t>regime DEEP-FAIL (-19.7291% vs the 200-day average) - watch only, no size; trend strength (ADX) 17.6438 below 20 - no trend to ride; sto...</t>
         </is>
       </c>
-      <c r="Z46" s="25" t="inlineStr"/>
+      <c r="Z46" s="25" t="n"/>
       <c r="AA46" s="25" t="inlineStr"/>
+      <c r="AB46" s="25" t="inlineStr"/>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="23" t="n">
@@ -37300,12 +37363,13 @@
           <t>price 129.575 at/below its trend line (ZLSMA) 129.7069 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z47" s="25" t="inlineStr">
+      <c r="Z47" s="25" t="n"/>
+      <c r="AA47" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="AA47" s="25" t="inlineStr">
+      <c r="AB47" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS -0.27). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -37401,8 +37465,9 @@
           <t>price 100.5175 at/below its trend line (ZLSMA) 107.1078 - structure has not turned; stop is 0.74x ATR (multiples of a normal day's swing) (3.2018) - inside dail...</t>
         </is>
       </c>
-      <c r="Z48" s="25" t="inlineStr"/>
+      <c r="Z48" s="25" t="n"/>
       <c r="AA48" s="25" t="inlineStr"/>
+      <c r="AB48" s="25" t="inlineStr"/>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="23" t="n">
@@ -37494,8 +37559,9 @@
           <t>price 151.1525 at/below its trend line (ZLSMA) 154.0157 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z49" s="25" t="inlineStr"/>
+      <c r="Z49" s="25" t="n"/>
       <c r="AA49" s="25" t="inlineStr"/>
+      <c r="AB49" s="25" t="inlineStr"/>
     </row>
     <row r="50" ht="45" customHeight="1">
       <c r="A50" s="23" t="n">
@@ -37577,8 +37643,9 @@
           <t>regime DEEP-FAIL (-11.3595% vs the 200-day average) - watch only, no size; price 28.31 at/below its trend line (ZLSMA) 28.5005 - structu...</t>
         </is>
       </c>
-      <c r="Z50" s="25" t="inlineStr"/>
+      <c r="Z50" s="25" t="n"/>
       <c r="AA50" s="25" t="inlineStr"/>
+      <c r="AB50" s="25" t="inlineStr"/>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="23" t="n">
@@ -37670,8 +37737,9 @@
           <t>price 387.9925 at/below its trend line (ZLSMA) 394.2479 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z51" s="25" t="inlineStr"/>
+      <c r="Z51" s="25" t="n"/>
       <c r="AA51" s="25" t="inlineStr"/>
+      <c r="AB51" s="25" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="23" t="n">
@@ -37769,8 +37837,9 @@
           <t>price 133.165 at/below its trend line (ZLSMA) 133.5495 - structure has not turned; stop is 0.78x ATR (multiples of a normal day's swing) (4.5202) - inside daily...</t>
         </is>
       </c>
-      <c r="Z52" s="25" t="inlineStr"/>
+      <c r="Z52" s="25" t="n"/>
       <c r="AA52" s="25" t="inlineStr"/>
+      <c r="AB52" s="25" t="inlineStr"/>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="23" t="n">
@@ -37852,8 +37921,9 @@
           <t>regime DEEP-FAIL (-14.2162% vs the 200-day average) - watch only, no size; price 121.0413 at/below its trend line (ZLSMA) 121.9243 - str...</t>
         </is>
       </c>
-      <c r="Z53" s="25" t="inlineStr"/>
+      <c r="Z53" s="25" t="n"/>
       <c r="AA53" s="25" t="inlineStr"/>
+      <c r="AB53" s="25" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="23" t="n">
@@ -37951,8 +38021,9 @@
           <t>price 596.5877 at/below its trend line (ZLSMA) 627.1908 - structure has not turned; stop is 0.29x ATR (multiples of a normal day's swing) (21.3648) - inside dai...</t>
         </is>
       </c>
-      <c r="Z54" s="25" t="inlineStr"/>
+      <c r="Z54" s="25" t="n"/>
       <c r="AA54" s="25" t="inlineStr"/>
+      <c r="AB54" s="25" t="inlineStr"/>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="23" t="n">
@@ -38044,12 +38115,13 @@
           <t>price 133.0125 at/below its trend line (ZLSMA) 133.9452 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z55" s="25" t="inlineStr">
+      <c r="Z55" s="25" t="n"/>
+      <c r="AA55" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="AA55" s="25" t="inlineStr">
+      <c r="AB55" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +0.60). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -38151,8 +38223,9 @@
           <t>trend strength (ADX) 15.0931 below 20 - no trend to ride; price 296.8964 at/below its trend line (ZLSMA) 311.9719 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z56" s="25" t="inlineStr"/>
+      <c r="Z56" s="25" t="n"/>
       <c r="AA56" s="25" t="inlineStr"/>
+      <c r="AB56" s="25" t="inlineStr"/>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="23" t="n">
@@ -38250,8 +38323,9 @@
           <t>trend strength (ADX) 19.2905 below 20 - no trend to ride; price 39.64 at/below its trend line (ZLSMA) 39.8437 - structure has not turned; sto...</t>
         </is>
       </c>
-      <c r="Z57" s="25" t="inlineStr"/>
+      <c r="Z57" s="25" t="n"/>
       <c r="AA57" s="25" t="inlineStr"/>
+      <c r="AB57" s="25" t="inlineStr"/>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="A58" s="23" t="n">
@@ -38343,8 +38417,9 @@
           <t>price 85.1313 at/below its trend line (ZLSMA) 85.5862 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z58" s="25" t="inlineStr"/>
+      <c r="Z58" s="25" t="n"/>
       <c r="AA58" s="25" t="inlineStr"/>
+      <c r="AB58" s="25" t="inlineStr"/>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="A59" s="23" t="n">
@@ -38442,8 +38517,9 @@
           <t>-DI 19.2266 &gt;= +DI 18.3181 - sellers in control; price 10.7 at/below its trend line (ZLSMA) 11.3595 - structure has not turn...</t>
         </is>
       </c>
-      <c r="Z59" s="25" t="inlineStr"/>
+      <c r="Z59" s="25" t="n"/>
       <c r="AA59" s="25" t="inlineStr"/>
+      <c r="AB59" s="25" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="23" t="n">
@@ -38535,12 +38611,13 @@
           <t>price 196.435 at/below its trend line (ZLSMA) 201.9239 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z60" s="25" t="inlineStr">
+      <c r="Z60" s="25" t="n"/>
+      <c r="AA60" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="AA60" s="25" t="inlineStr">
+      <c r="AB60" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +0.47). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -38642,8 +38719,9 @@
           <t>-DI 21.6818 &gt;= +DI 16.4664 - sellers in control; price 179.3075 at/below its trend line (ZLSMA) 183.5418 - structure has not...</t>
         </is>
       </c>
-      <c r="Z61" s="25" t="inlineStr"/>
+      <c r="Z61" s="25" t="n"/>
       <c r="AA61" s="25" t="inlineStr"/>
+      <c r="AB61" s="25" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="23" t="n">
@@ -38735,12 +38813,13 @@
           <t>trend strength (ADX) 16.1122 below 20 - no trend to ride; price 188.3075 at/below its trend line (ZLSMA) 189.3949 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z62" s="25" t="inlineStr">
+      <c r="Z62" s="25" t="n"/>
+      <c r="AA62" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="AA62" s="25" t="inlineStr">
+      <c r="AB62" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS n/a). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -38836,8 +38915,9 @@
           <t>price 341.1725 at/below its trend line (ZLSMA) 345.7113 - structure has not turned; stop is 0.74x ATR (multiples of a normal day's swing) (13.1473) - inside dai...</t>
         </is>
       </c>
-      <c r="Z63" s="25" t="inlineStr"/>
+      <c r="Z63" s="25" t="n"/>
       <c r="AA63" s="25" t="inlineStr"/>
+      <c r="AB63" s="25" t="inlineStr"/>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="23" t="n">
@@ -38929,8 +39009,9 @@
           <t>price 211.5075 at/below its trend line (ZLSMA) 218.7627 - structure has not turned; stop is 0.78x ATR (multiples of a normal day's swing) (9.071) - inside daily...</t>
         </is>
       </c>
-      <c r="Z64" s="25" t="inlineStr"/>
+      <c r="Z64" s="25" t="n"/>
       <c r="AA64" s="25" t="inlineStr"/>
+      <c r="AB64" s="25" t="inlineStr"/>
     </row>
     <row r="65" ht="45" customHeight="1">
       <c r="A65" s="23" t="n">
@@ -39028,8 +39109,9 @@
           <t>trend strength (ADX) 16.9636 below 20 - no trend to ride; -DI 20.7364 &gt;= +DI 18.12 - sellers in control; price 350.3325 at/b...</t>
         </is>
       </c>
-      <c r="Z65" s="25" t="inlineStr"/>
+      <c r="Z65" s="25" t="n"/>
       <c r="AA65" s="25" t="inlineStr"/>
+      <c r="AB65" s="25" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="23" t="n">
@@ -39121,12 +39203,13 @@
           <t>price 523.136 at/below its trend line (ZLSMA) 535.5478 - structure has not turned; stop is 0.97x ATR (multiples of a normal day's swing) (33.2767) - inside dail...</t>
         </is>
       </c>
-      <c r="Z66" s="25" t="inlineStr">
+      <c r="Z66" s="25" t="n"/>
+      <c r="AA66" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="AA66" s="25" t="inlineStr">
+      <c r="AB66" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +1.84). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -39222,12 +39305,13 @@
           <t>regime DEEP-FAIL (-23.1574% vs the 200-day average) - watch only, no size; price 63.0125 at/below its trend line (ZLSMA) 69.9927 - struc...</t>
         </is>
       </c>
-      <c r="Z67" s="25" t="inlineStr">
+      <c r="Z67" s="25" t="n"/>
+      <c r="AA67" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="AA67" s="25" t="inlineStr">
+      <c r="AB67" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +0.31). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -39329,8 +39413,9 @@
           <t>trend strength (ADX) 16.123 below 20 - no trend to ride; -DI 16.4196 &gt;= +DI 15.6242 - sellers in control; price 971.9825 at/...</t>
         </is>
       </c>
-      <c r="Z68" s="25" t="inlineStr"/>
+      <c r="Z68" s="25" t="n"/>
       <c r="AA68" s="25" t="inlineStr"/>
+      <c r="AB68" s="25" t="inlineStr"/>
     </row>
     <row r="69" ht="45" customHeight="1">
       <c r="A69" s="23" t="n">
@@ -39422,8 +39507,9 @@
           <t>price 139.405 at/below its trend line (ZLSMA) 140.6837 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z69" s="25" t="inlineStr"/>
+      <c r="Z69" s="25" t="n"/>
       <c r="AA69" s="25" t="inlineStr"/>
+      <c r="AB69" s="25" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="23" t="n">
@@ -39521,8 +39607,9 @@
           <t>price 186.8038 at/below its trend line (ZLSMA) 189.1902 - structure has not turned; stop is 0.44x ATR (multiples of a normal day's swing) (7.4025) - inside dail...</t>
         </is>
       </c>
-      <c r="Z70" s="25" t="inlineStr"/>
+      <c r="Z70" s="25" t="n"/>
       <c r="AA70" s="25" t="inlineStr"/>
+      <c r="AB70" s="25" t="inlineStr"/>
     </row>
     <row r="71" ht="45" customHeight="1">
       <c r="A71" s="23" t="n">
@@ -39620,8 +39707,9 @@
           <t>-DI 21.4858 &gt;= +DI 18.3012 - sellers in control; price 111.17 at/below its trend line (ZLSMA) 112.5104 - structure has not t...</t>
         </is>
       </c>
-      <c r="Z71" s="25" t="inlineStr"/>
+      <c r="Z71" s="25" t="n"/>
       <c r="AA71" s="25" t="inlineStr"/>
+      <c r="AB71" s="25" t="inlineStr"/>
     </row>
     <row r="72" ht="45" customHeight="1">
       <c r="A72" s="23" t="n">
@@ -39713,8 +39801,9 @@
           <t>regime DEEP-FAIL (-16.4518% vs the 200-day average) - watch only, no size; trend strength (ADX) 18.6733 below 20 - no trend to ride; pri...</t>
         </is>
       </c>
-      <c r="Z72" s="25" t="inlineStr"/>
+      <c r="Z72" s="25" t="n"/>
       <c r="AA72" s="25" t="inlineStr"/>
+      <c r="AB72" s="25" t="inlineStr"/>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="23" t="n">
@@ -39806,8 +39895,9 @@
           <t>trend strength (ADX) 10.1704 below 20 - no trend to ride; price 21.8037 at/below its trend line (ZLSMA) 22.658 - structure has not turned</t>
         </is>
       </c>
-      <c r="Z73" s="25" t="inlineStr"/>
+      <c r="Z73" s="25" t="n"/>
       <c r="AA73" s="25" t="inlineStr"/>
+      <c r="AB73" s="25" t="inlineStr"/>
     </row>
     <row r="74" ht="45" customHeight="1">
       <c r="A74" s="23" t="n">
@@ -39889,8 +39979,9 @@
           <t>regime DEEP-FAIL (-11.8072% vs the 200-day average) - watch only, no size; price 4.875 at/below its trend line (ZLSMA) 4.9064 - structur...</t>
         </is>
       </c>
-      <c r="Z74" s="25" t="inlineStr"/>
+      <c r="Z74" s="25" t="n"/>
       <c r="AA74" s="25" t="inlineStr"/>
+      <c r="AB74" s="25" t="inlineStr"/>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="23" t="n">
@@ -39982,12 +40073,13 @@
           <t>trend strength (ADX) 11.9623 below 20 - no trend to ride; price 95.4125 at/below its trend line (ZLSMA) 95.4299 - structure has not turned; s...</t>
         </is>
       </c>
-      <c r="Z75" s="25" t="inlineStr">
+      <c r="Z75" s="25" t="n"/>
+      <c r="AA75" s="25" t="inlineStr">
         <is>
           <t>Earnings 2026-08-03</t>
         </is>
       </c>
-      <c r="AA75" s="25" t="inlineStr">
+      <c r="AB75" s="25" t="inlineStr">
         <is>
           <t>Reports 2026-08-03 (est EPS +1.64). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -40083,8 +40175,9 @@
           <t>trend strength (ADX) 14.7655 below 20 - no trend to ride; -DI 18.0212 &gt;= +DI 17.4126 - sellers in control; price 331.7976 at...</t>
         </is>
       </c>
-      <c r="Z76" s="25" t="inlineStr"/>
+      <c r="Z76" s="25" t="n"/>
       <c r="AA76" s="25" t="inlineStr"/>
+      <c r="AB76" s="25" t="inlineStr"/>
     </row>
     <row r="77" ht="45" customHeight="1">
       <c r="A77" s="23" t="n">
@@ -40176,8 +40269,9 @@
           <t>trend strength (ADX) 13.8388 below 20 - no trend to ride; -DI 21.9574 &gt;= +DI 16.4501 - sellers in control; price 18.7225 at/...</t>
         </is>
       </c>
-      <c r="Z77" s="25" t="inlineStr"/>
+      <c r="Z77" s="25" t="n"/>
       <c r="AA77" s="25" t="inlineStr"/>
+      <c r="AB77" s="25" t="inlineStr"/>
     </row>
     <row r="78" ht="45" customHeight="1">
       <c r="A78" s="23" t="n">
@@ -40269,8 +40363,9 @@
           <t>regime DEEP-FAIL (-30.9453% vs the 200-day average) - watch only, no size; trend strength (ADX) 17.7745 below 20 - no trend to ride; -DI...</t>
         </is>
       </c>
-      <c r="Z78" s="25" t="inlineStr"/>
+      <c r="Z78" s="25" t="n"/>
       <c r="AA78" s="25" t="inlineStr"/>
+      <c r="AB78" s="25" t="inlineStr"/>
     </row>
     <row r="79" ht="45" customHeight="1">
       <c r="A79" s="23" t="n">
@@ -40362,11 +40457,12 @@
           <t>regime DEEP-FAIL (-13.1518% vs the 200-day average) - watch only, no size; trend strength (ADX) 16.3357 below 20 - no trend to ride; -DI...</t>
         </is>
       </c>
-      <c r="Z79" s="25" t="inlineStr"/>
+      <c r="Z79" s="25" t="n"/>
       <c r="AA79" s="25" t="inlineStr"/>
+      <c r="AB79" s="25" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -40378,7 +40474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40393,8 +40489,9 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="62" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -40460,10 +40557,15 @@
       </c>
       <c r="M1" s="12" t="inlineStr">
         <is>
+          <t>Rested Leader</t>
+        </is>
+      </c>
+      <c r="N1" s="12" t="inlineStr">
+        <is>
           <t>Catalyst</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>Catalyst View</t>
         </is>
@@ -40514,12 +40616,13 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (-3.5624% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M2" s="19" t="inlineStr">
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="N2" s="19" t="inlineStr">
+      <c r="O2" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +0.68). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -40570,8 +40673,9 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (-3.4519% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr"/>
+      <c r="M3" s="19" t="n"/>
       <c r="N3" s="19" t="inlineStr"/>
+      <c r="O3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="17" t="n">
@@ -40618,8 +40722,9 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (-1.0484% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M4" s="19" t="inlineStr"/>
+      <c r="M4" s="19" t="n"/>
       <c r="N4" s="19" t="inlineStr"/>
+      <c r="O4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="17" t="n">
@@ -40666,8 +40771,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr"/>
+      <c r="M5" s="19" t="n"/>
       <c r="N5" s="19" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="17" t="n">
@@ -40714,12 +40820,13 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (3.8185% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="N6" s="19" t="inlineStr">
+      <c r="O6" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +3.85). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -40770,8 +40877,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr"/>
+      <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="17" t="n">
@@ -40818,8 +40926,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M8" s="19" t="inlineStr"/>
+      <c r="M8" s="19" t="n"/>
       <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="17" t="n">
@@ -40866,8 +40975,9 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (8.4497% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr"/>
+      <c r="M9" s="19" t="n"/>
       <c r="N9" s="19" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="17" t="n">
@@ -40914,8 +41024,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr"/>
+      <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="17" t="n">
@@ -40962,8 +41073,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr"/>
+      <c r="M11" s="19" t="n"/>
       <c r="N11" s="19" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="17" t="n">
@@ -41010,8 +41122,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr"/>
+      <c r="M12" s="19" t="n"/>
       <c r="N12" s="19" t="inlineStr"/>
+      <c r="O12" s="19" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="17" t="n">
@@ -41058,12 +41171,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +5.62). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -41114,8 +41228,9 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (11.8104% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M14" s="19" t="inlineStr"/>
+      <c r="M14" s="19" t="n"/>
       <c r="N14" s="19" t="inlineStr"/>
+      <c r="O14" s="19" t="inlineStr"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="17" t="n">
@@ -41162,8 +41277,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr"/>
+      <c r="M15" s="19" t="inlineStr">
+        <is>
+          <t>RESTED LEADER - on trial</t>
+        </is>
+      </c>
       <c r="N15" s="19" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="17" t="n">
@@ -41210,8 +41330,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M16" s="19" t="inlineStr"/>
+      <c r="M16" s="19" t="n"/>
       <c r="N16" s="19" t="inlineStr"/>
+      <c r="O16" s="19" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="17" t="n">
@@ -41258,12 +41379,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M17" s="19" t="inlineStr">
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="N17" s="19" t="inlineStr">
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +0.20). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -41314,8 +41436,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr"/>
+      <c r="M18" s="19" t="n"/>
       <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="19" t="inlineStr"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="17" t="n">
@@ -41362,8 +41485,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M19" s="19" t="inlineStr"/>
+      <c r="M19" s="19" t="inlineStr">
+        <is>
+          <t>RESTED LEADER - on trial</t>
+        </is>
+      </c>
       <c r="N19" s="19" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="17" t="n">
@@ -41410,8 +41538,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M20" s="19" t="inlineStr"/>
+      <c r="M20" s="19" t="n"/>
       <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="17" t="n">
@@ -41458,12 +41587,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-03</t>
         </is>
       </c>
-      <c r="N21" s="19" t="inlineStr">
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-03 (est EPS +6.08). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -41514,12 +41644,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-04</t>
         </is>
       </c>
-      <c r="N22" s="19" t="inlineStr">
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-04 (est EPS +5.00). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -41570,8 +41701,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M23" s="19" t="inlineStr"/>
+      <c r="M23" s="19" t="n"/>
       <c r="N23" s="19" t="inlineStr"/>
+      <c r="O23" s="19" t="inlineStr"/>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="17" t="n">
@@ -41618,8 +41750,9 @@
           <t>STARTER (regime REPAIR - half size). regime REPAIR (23.0346% vs the 200-day average) - starter size only</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr"/>
+      <c r="M24" s="19" t="n"/>
       <c r="N24" s="19" t="inlineStr"/>
+      <c r="O24" s="19" t="inlineStr"/>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="17" t="n">
@@ -41666,8 +41799,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M25" s="19" t="inlineStr"/>
+      <c r="M25" s="19" t="n"/>
       <c r="N25" s="19" t="inlineStr"/>
+      <c r="O25" s="19" t="inlineStr"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="17" t="n">
@@ -41714,8 +41848,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M26" s="19" t="inlineStr"/>
+      <c r="M26" s="19" t="n"/>
       <c r="N26" s="19" t="inlineStr"/>
+      <c r="O26" s="19" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="17" t="n">
@@ -41762,8 +41897,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M27" s="19" t="inlineStr"/>
+      <c r="M27" s="19" t="n"/>
       <c r="N27" s="19" t="inlineStr"/>
+      <c r="O27" s="19" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="17" t="n">
@@ -41810,8 +41946,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr"/>
+      <c r="M28" s="19" t="n"/>
       <c r="N28" s="19" t="inlineStr"/>
+      <c r="O28" s="19" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="17" t="n">
@@ -41858,12 +41995,13 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M29" s="19" t="inlineStr">
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="inlineStr">
         <is>
           <t>Earnings 2026-08-05</t>
         </is>
       </c>
-      <c r="N29" s="19" t="inlineStr">
+      <c r="O29" s="19" t="inlineStr">
         <is>
           <t>Reports 2026-08-05 (est EPS +2.25). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
@@ -41914,8 +42052,9 @@
           <t>Passes every gate.</t>
         </is>
       </c>
-      <c r="M30" s="19" t="inlineStr"/>
+      <c r="M30" s="19" t="n"/>
       <c r="N30" s="19" t="inlineStr"/>
+      <c r="O30" s="19" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -42011,7 +42150,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
